--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/documentation/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2701F777-FBDF-7547-B1F1-A972034D1B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FF6C31-6D7C-2C4A-8137-6504F96380A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,9 +350,6 @@
     <t>2026-05-05</t>
   </si>
   <si>
-    <t>v1</t>
-  </si>
-  <si>
     <t>France</t>
   </si>
   <si>
@@ -483,6 +480,9 @@
   </si>
   <si>
     <t>Product testing with users in agriculture and food: Decentralized on-farm evaluation, breeding product validation, consumer testing and other applications using the tricot approach</t>
+  </si>
+  <si>
+    <t>v1.1</t>
   </si>
 </sst>
 </file>
@@ -912,7 +912,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -920,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -944,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1054,10 +1054,10 @@
         <v>42</v>
       </c>
       <c r="H2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" t="s">
         <v>108</v>
-      </c>
-      <c r="I2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1077,10 +1077,10 @@
         <v>42</v>
       </c>
       <c r="H3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" t="s">
         <v>108</v>
-      </c>
-      <c r="I3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -1100,18 +1100,18 @@
         <v>42</v>
       </c>
       <c r="H4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" t="s">
         <v>108</v>
-      </c>
-      <c r="I4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
         <v>110</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
@@ -1120,10 +1120,10 @@
         <v>102</v>
       </c>
       <c r="H5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" t="s">
         <v>112</v>
-      </c>
-      <c r="I5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1143,18 +1143,18 @@
         <v>42</v>
       </c>
       <c r="H6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" t="s">
         <v>108</v>
-      </c>
-      <c r="I6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
         <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
       </c>
       <c r="D7" t="s">
         <v>75</v>
@@ -1163,21 +1163,21 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" t="s">
         <v>108</v>
-      </c>
-      <c r="I7" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
         <v>116</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>117</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>75</v>
@@ -1186,33 +1186,33 @@
         <v>52</v>
       </c>
       <c r="H8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" t="s">
         <v>119</v>
-      </c>
-      <c r="I8" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" t="s">
         <v>121</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>122</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
         <v>123</v>
       </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>124</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>125</v>
-      </c>
-      <c r="I9" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -1232,10 +1232,10 @@
         <v>42</v>
       </c>
       <c r="H10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" t="s">
         <v>108</v>
-      </c>
-      <c r="I10" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1255,10 +1255,10 @@
         <v>58</v>
       </c>
       <c r="H11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" t="s">
         <v>127</v>
-      </c>
-      <c r="I11" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1278,18 +1278,18 @@
         <v>52</v>
       </c>
       <c r="H12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
         <v>129</v>
-      </c>
-      <c r="I12" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s">
         <v>131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>132</v>
       </c>
       <c r="D13" t="s">
         <v>75</v>
@@ -1298,10 +1298,10 @@
         <v>42</v>
       </c>
       <c r="H13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" t="s">
         <v>108</v>
-      </c>
-      <c r="I13" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1318,18 +1318,18 @@
         <v>102</v>
       </c>
       <c r="H14" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" t="s">
         <v>112</v>
-      </c>
-      <c r="I14" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
         <v>133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>134</v>
       </c>
       <c r="D15" t="s">
         <v>75</v>
@@ -1338,21 +1338,21 @@
         <v>102</v>
       </c>
       <c r="H15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" t="s">
         <v>112</v>
-      </c>
-      <c r="I15" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" t="s">
         <v>135</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>136</v>
-      </c>
-      <c r="C16" t="s">
-        <v>137</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -1361,10 +1361,10 @@
         <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1372,10 +1372,10 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" t="s">
         <v>138</v>
-      </c>
-      <c r="C17" t="s">
-        <v>139</v>
       </c>
       <c r="D17" t="s">
         <v>75</v>
@@ -1384,10 +1384,10 @@
         <v>42</v>
       </c>
       <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" t="s">
         <v>108</v>
-      </c>
-      <c r="I17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1407,30 +1407,30 @@
         <v>42</v>
       </c>
       <c r="H18" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" t="s">
         <v>140</v>
-      </c>
-      <c r="I18" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" t="s">
         <v>142</v>
       </c>
-      <c r="B19" t="s">
-        <v>143</v>
-      </c>
       <c r="D19" t="s">
         <v>75</v>
       </c>
       <c r="E19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" t="s">
         <v>124</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1450,10 +1450,10 @@
         <v>48</v>
       </c>
       <c r="H20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" t="s">
         <v>144</v>
-      </c>
-      <c r="I20" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1473,21 +1473,21 @@
         <v>58</v>
       </c>
       <c r="H21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" t="s">
         <v>127</v>
-      </c>
-      <c r="I21" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s">
         <v>146</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>147</v>
-      </c>
-      <c r="C22" t="s">
-        <v>148</v>
       </c>
       <c r="D22" t="s">
         <v>75</v>
@@ -1496,10 +1496,10 @@
         <v>52</v>
       </c>
       <c r="H22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" t="s">
         <v>119</v>
-      </c>
-      <c r="I22" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1519,10 +1519,10 @@
         <v>42</v>
       </c>
       <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" t="s">
         <v>108</v>
-      </c>
-      <c r="I23" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="80" spans="3:3" x14ac:dyDescent="0.2">
@@ -1720,7 +1720,7 @@
         <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>39</v>
